--- a/public/files/one-term-ai-education-plan.xlsx
+++ b/public/files/one-term-ai-education-plan.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -727,20 +727,6 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>官方文件參考：《中小學數字教育發展藍圖》（三摺頁，p.2）要求在學校發展計劃中加入數碼與 AI 教育策略，並附清晰的實施時間表；《中小學人工智能素養學習架構》（pp.1-6 to 1-10）訂出跨科實施與四個學習階段的進程。</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>本檔為 Beets 獨立製作的教學資源，並非 EDB 官方文件。</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
           <t>如對本資源有任何意見或疑問，歡迎電郵至 enquiry@beets-ai.com</t>
         </is>
       </c>

--- a/public/files/one-term-ai-education-plan.xlsx
+++ b/public/files/one-term-ai-education-plan.xlsx
@@ -479,6 +479,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -487,12 +488,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>負責人</t>
+          <t>負責人 Owner</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>日期／週次</t>
+          <t>日期／週次 Dates / week</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -519,6 +520,7 @@
       <c r="C8" s="3" t="inlineStr"/>
       <c r="D8" s="3" t="inlineStr"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -526,6 +528,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -629,6 +632,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
@@ -637,12 +641,12 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>負責人</t>
+          <t>負責人 Owner</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>日期／週次</t>
+          <t>日期／週次 Dates / week</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -717,6 +721,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -724,6 +729,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
